--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-compatible-with-import.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-compatible-with-import.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t xml:space="preserve">SAMPLE_TYPE</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Type Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta Data</t>
   </si>
   <si>
     <t xml:space="preserve">ENTRY</t>
@@ -152,7 +155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -177,6 +180,14 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -230,7 +241,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -239,7 +250,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -261,7 +276,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -299,29 +314,32 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -331,46 +349,46 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>7</v>
@@ -383,135 +401,135 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-compatible-with-import.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-compatible-with-import.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Ontology Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Type Group</t>
+    <t xml:space="preserve">Type Groups</t>
   </si>
   <si>
     <t xml:space="preserve">Meta Data</t>
@@ -155,7 +155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -196,6 +196,28 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -241,7 +263,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -255,6 +277,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -275,8 +313,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S1048576"/>
+  <sheetFormatPr defaultColWidth="10.859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -318,7 +356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -340,6 +378,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -531,6 +570,28 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
